--- a/exports/website_analytics_complete.xlsx
+++ b/exports/website_analytics_complete.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="191">
   <si>
     <t>Visitor ID</t>
   </si>
@@ -226,6 +226,9 @@
     <t>2026-09-10 23:23:04</t>
   </si>
   <si>
+    <t>2026-09-11 12:13:39</t>
+  </si>
+  <si>
     <t>test-auto-export-visitor</t>
   </si>
   <si>
@@ -419,6 +422,15 @@
   </si>
   <si>
     <t>2026-09-10 23:32:58</t>
+  </si>
+  <si>
+    <t>/test-page</t>
+  </si>
+  <si>
+    <t>2026-09-11 11:40:07</t>
+  </si>
+  <si>
+    <t>2026-09-11 12:13:47</t>
   </si>
   <si>
     <t>Lead Source</t>
@@ -1111,12 +1123,12 @@
         <v>69</v>
       </c>
       <c r="I15" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s" s="0">
         <v>14</v>
@@ -1137,10 +1149,10 @@
         <v>15</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1150,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.40625" customWidth="true" bestFit="true"/>
@@ -1168,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s" s="2">
         <v>1</v>
@@ -1186,7 +1198,7 @@
         <v>5</v>
       </c>
       <c r="H1" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2">
@@ -1194,10 +1206,10 @@
         <v>9</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>10</v>
@@ -1212,7 +1224,7 @@
         <v>14</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -1220,10 +1232,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>10</v>
@@ -1238,7 +1250,7 @@
         <v>14</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -1246,10 +1258,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>10</v>
@@ -1264,7 +1276,7 @@
         <v>14</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -1272,10 +1284,10 @@
         <v>18</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>14</v>
@@ -1298,10 +1310,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>14</v>
@@ -1324,10 +1336,10 @@
         <v>23</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>24</v>
@@ -1342,7 +1354,7 @@
         <v>14</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -1350,10 +1362,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>10</v>
@@ -1368,7 +1380,7 @@
         <v>14</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -1376,10 +1388,10 @@
         <v>18</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>14</v>
@@ -1402,10 +1414,10 @@
         <v>18</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>14</v>
@@ -1428,10 +1440,10 @@
         <v>23</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>24</v>
@@ -1446,7 +1458,7 @@
         <v>14</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
@@ -1454,10 +1466,10 @@
         <v>29</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>14</v>
@@ -1472,7 +1484,7 @@
         <v>14</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -1480,10 +1492,10 @@
         <v>31</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>14</v>
@@ -1498,7 +1510,7 @@
         <v>14</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1506,10 +1518,10 @@
         <v>33</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>14</v>
@@ -1532,10 +1544,10 @@
         <v>35</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s" s="0">
         <v>14</v>
@@ -1550,7 +1562,7 @@
         <v>14</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -1558,10 +1570,10 @@
         <v>35</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>14</v>
@@ -1576,7 +1588,7 @@
         <v>14</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
@@ -1584,10 +1596,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>40</v>
@@ -1602,7 +1614,7 @@
         <v>14</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
@@ -1610,10 +1622,10 @@
         <v>39</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>40</v>
@@ -1628,7 +1640,7 @@
         <v>14</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19">
@@ -1636,10 +1648,10 @@
         <v>39</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>40</v>
@@ -1654,7 +1666,7 @@
         <v>14</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
@@ -1662,10 +1674,10 @@
         <v>39</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>40</v>
@@ -1680,7 +1692,7 @@
         <v>14</v>
       </c>
       <c r="H20" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21">
@@ -1688,10 +1700,10 @@
         <v>39</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>40</v>
@@ -1706,7 +1718,7 @@
         <v>14</v>
       </c>
       <c r="H21" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22">
@@ -1714,10 +1726,10 @@
         <v>39</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>40</v>
@@ -1732,7 +1744,7 @@
         <v>14</v>
       </c>
       <c r="H22" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23">
@@ -1740,10 +1752,10 @@
         <v>45</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>46</v>
@@ -1758,7 +1770,7 @@
         <v>14</v>
       </c>
       <c r="H23" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
@@ -1766,10 +1778,10 @@
         <v>45</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>46</v>
@@ -1784,7 +1796,7 @@
         <v>14</v>
       </c>
       <c r="H24" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25">
@@ -1792,10 +1804,10 @@
         <v>45</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>46</v>
@@ -1810,7 +1822,7 @@
         <v>14</v>
       </c>
       <c r="H25" t="s" s="0">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
@@ -1818,10 +1830,10 @@
         <v>45</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s" s="0">
         <v>46</v>
@@ -1836,7 +1848,7 @@
         <v>14</v>
       </c>
       <c r="H26" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27">
@@ -1844,10 +1856,10 @@
         <v>52</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>53</v>
@@ -1862,7 +1874,7 @@
         <v>14</v>
       </c>
       <c r="H27" t="s" s="0">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28">
@@ -1870,10 +1882,10 @@
         <v>52</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>53</v>
@@ -1888,7 +1900,7 @@
         <v>14</v>
       </c>
       <c r="H28" t="s" s="0">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
@@ -1896,10 +1908,10 @@
         <v>52</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>53</v>
@@ -1914,7 +1926,7 @@
         <v>14</v>
       </c>
       <c r="H29" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30">
@@ -1922,10 +1934,10 @@
         <v>52</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>53</v>
@@ -1940,7 +1952,7 @@
         <v>14</v>
       </c>
       <c r="H30" t="s" s="0">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31">
@@ -1948,10 +1960,10 @@
         <v>58</v>
       </c>
       <c r="B31" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>59</v>
@@ -1966,7 +1978,7 @@
         <v>14</v>
       </c>
       <c r="H31" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32">
@@ -1974,10 +1986,10 @@
         <v>58</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>59</v>
@@ -1992,7 +2004,7 @@
         <v>14</v>
       </c>
       <c r="H32" t="s" s="0">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33">
@@ -2000,10 +2012,10 @@
         <v>58</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s" s="0">
         <v>59</v>
@@ -2018,7 +2030,7 @@
         <v>14</v>
       </c>
       <c r="H33" t="s" s="0">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34">
@@ -2026,10 +2038,10 @@
         <v>58</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s" s="0">
         <v>59</v>
@@ -2044,7 +2056,7 @@
         <v>14</v>
       </c>
       <c r="H34" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35">
@@ -2052,10 +2064,10 @@
         <v>58</v>
       </c>
       <c r="B35" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s" s="0">
         <v>59</v>
@@ -2070,7 +2082,7 @@
         <v>14</v>
       </c>
       <c r="H35" t="s" s="0">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36">
@@ -2078,10 +2090,10 @@
         <v>66</v>
       </c>
       <c r="B36" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>14</v>
@@ -2096,7 +2108,7 @@
         <v>14</v>
       </c>
       <c r="H36" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37">
@@ -2104,10 +2116,10 @@
         <v>66</v>
       </c>
       <c r="B37" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>14</v>
@@ -2122,7 +2134,7 @@
         <v>14</v>
       </c>
       <c r="H37" t="s" s="0">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
@@ -2130,10 +2142,10 @@
         <v>68</v>
       </c>
       <c r="B38" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>14</v>
@@ -2148,7 +2160,7 @@
         <v>14</v>
       </c>
       <c r="H38" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39">
@@ -2156,10 +2168,10 @@
         <v>68</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>14</v>
@@ -2174,7 +2186,7 @@
         <v>14</v>
       </c>
       <c r="H39" t="s" s="0">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
@@ -2182,10 +2194,10 @@
         <v>68</v>
       </c>
       <c r="B40" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>14</v>
@@ -2200,18 +2212,18 @@
         <v>14</v>
       </c>
       <c r="H40" t="s" s="0">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s" s="0">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D41" t="s" s="0">
         <v>14</v>
@@ -2226,18 +2238,18 @@
         <v>14</v>
       </c>
       <c r="H41" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B42" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D42" t="s" s="0">
         <v>14</v>
@@ -2252,7 +2264,59 @@
         <v>14</v>
       </c>
       <c r="H42" t="s" s="0">
-        <v>134</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="F43" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E44" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="F44" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="G44" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H44" t="s" s="0">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2293,13 +2357,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G1" t="s" s="3">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H1" t="s" s="3">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I1" t="s" s="3">
         <v>6</v>
@@ -2322,13 +2386,13 @@
         <v>13</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I2" t="s" s="0">
         <v>15</v>
@@ -2351,13 +2415,13 @@
         <v>27</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I3" t="s" s="0">
         <v>15</v>
@@ -2365,28 +2429,28 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F4" t="s" s="0">
         <v>142</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="G4" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="H4" t="s" s="0">
         <v>144</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>145</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>138</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>139</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>140</v>
       </c>
       <c r="I4" t="s" s="0">
         <v>15</v>
@@ -2400,22 +2464,22 @@
         <v>24</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I5" t="s" s="0">
         <v>15</v>
@@ -2438,13 +2502,13 @@
         <v>14</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>14</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I6" t="s" s="0">
         <v>15</v>
@@ -2458,7 +2522,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>14</v>
@@ -2467,13 +2531,13 @@
         <v>14</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G7" t="s" s="0">
         <v>14</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I7" t="s" s="0">
         <v>15</v>
@@ -2496,13 +2560,13 @@
         <v>43</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I8" t="s" s="0">
         <v>15</v>
@@ -2516,7 +2580,7 @@
         <v>14</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>14</v>
@@ -2525,13 +2589,13 @@
         <v>14</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G9" t="s" s="0">
         <v>14</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I9" t="s" s="0">
         <v>15</v>
@@ -2554,13 +2618,13 @@
         <v>49</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G10" t="s" s="0">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H10" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I10" t="s" s="0">
         <v>15</v>
@@ -2574,7 +2638,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>14</v>
@@ -2583,13 +2647,13 @@
         <v>14</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G11" t="s" s="0">
         <v>14</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I11" t="s" s="0">
         <v>15</v>
@@ -2612,13 +2676,13 @@
         <v>56</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G12" t="s" s="0">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H12" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I12" t="s" s="0">
         <v>15</v>
@@ -2632,22 +2696,22 @@
         <v>59</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>62</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G13" t="s" s="0">
         <v>14</v>
       </c>
       <c r="H13" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I13" t="s" s="0">
         <v>64</v>
@@ -2670,13 +2734,13 @@
         <v>62</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H14" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I14" t="s" s="0">
         <v>64</v>
@@ -2684,28 +2748,28 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="0">
         <v>10</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>13</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G15" t="s" s="0">
         <v>14</v>
       </c>
       <c r="H15" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I15" t="s" s="0">
         <v>15</v>
@@ -2713,28 +2777,28 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H16" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I16" t="s" s="0">
         <v>15</v>
@@ -2742,28 +2806,28 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H17" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I17" t="s" s="0">
         <v>15</v>
@@ -2771,28 +2835,28 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G18" t="s" s="0">
         <v>14</v>
       </c>
       <c r="H18" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I18" t="s" s="0">
         <v>15</v>
@@ -2800,28 +2864,28 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G19" t="s" s="0">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H19" t="s" s="0">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I19" t="s" s="0">
         <v>15</v>
